--- a/sample-exports/Root_inventory_fixture.xlsx
+++ b/sample-exports/Root_inventory_fixture.xlsx
@@ -52,7 +52,7 @@
     <t>Started</t>
   </si>
   <si>
-    <t>2026-10-24 17:44</t>
+    <t>2026-10-24 18:21</t>
   </si>
   <si>
     <t>Completed</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8 ms</t>
+    <t>6 ms</t>
   </si>
   <si>
     <t>Files</t>
